--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-specimen-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-specimen-pathology.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1736" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1736" uniqueCount="327">
   <si>
     <t>Property</t>
   </si>
@@ -42,13 +42,13 @@
     <t>Title</t>
   </si>
   <si>
-    <t>JP Specimen Pathology Profile</t>
+    <t>JP Core Specimen Pathology Profile</t>
   </si>
   <si>
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T12:23:16+00:00</t>
+    <t>2026-08-10T12:51:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>病理検体を表現するためのプロファイル。病理診断レポートのユースケースでは、臓器そのものを表現する。</t>
+    <t>病理診断レポートにおいて臓器そのものを表現する検体情報を定義したプロファイル</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -259,7 +259,7 @@
 </t>
   </si>
   <si>
-    <t>病理検体</t>
+    <t>病理診断レポートにおいて臓器そのものを表現する検体情報</t>
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
@@ -591,10 +591,7 @@
 </t>
   </si>
   <si>
-    <t>この標本が発生した標本 / Specimen from which this specimen originated</t>
-  </si>
-  <si>
-    <t>標本が別の標本の成分から由来するときに使用されるときに使用される親（ソース）標本への参照。 / Reference to the parent (source) specimen which is used when the specimen was either derived from or a component of another specimen.</t>
+    <t>使用しない</t>
   </si>
   <si>
     <t>親標本は、現在の標本が何らかの処理ステップ（例えば、臨床サンプルからアリコートまたは分離または抽出された核酸）またはプールされたサンプルを作成する多くの標本の1つによって導出される源である可能性があります。 / The parent specimen could be the source from which the current specimen is derived by some processing step (e.g. an aliquot or isolate or extracted nucleic acids from clinical samples) or one of many specimens that were combined to create a pooled sample.</t>
@@ -606,7 +603,7 @@
     <t>Specimen.request</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_ServiceRequest_Common)
+    <t xml:space="preserve">Reference(ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -632,10 +629,7 @@
 </t>
   </si>
   <si>
-    <t>コレクションの詳細 / Collection details</t>
-  </si>
-  <si>
-    <t>標本コレクションに関する詳細。 / Details concerning the specimen collection.</t>
+    <t>検体採取に関する詳細情報</t>
   </si>
   <si>
     <t>.participation[typeCode=SBJ].act[classCode=SPECCOLLECT, moodCode=EVN]</t>
@@ -800,12 +794,6 @@
 Duration</t>
   </si>
   <si>
-    <t>患者が食べ物や飲み物を控えているかどうか、またはどのくらいの期間 / Whether or how long patient abstained from food and/or drink</t>
-  </si>
-  <si>
-    <t>サンプル収集の前に、一部またはすべての食べ物、飲み物、またはその両方からの禁欲または削減。 / Abstinence or reduction from some or all food, drink, or both, for a period of time prior to sample collection.</t>
-  </si>
-  <si>
     <t>この要素を使用して絶食ステータスを表すことは、2時間の尿-12時間の断食でのLOINC 2005-7（カルシウム[モル/時間]）などの「事前調整コード」を使用して観察することでそれを表現することを好むか、またはコンポーネントの観測 `などの` observation.component code` = loinc 49541-6（空腹時ステータス - 報告）。 / Representing fasting status using this element is preferred to representing it with an observation using a 'pre-coordinated code'  such as  LOINC 2005-7 (Calcium [Moles/​time] in 2 hour Urine --12 hours fasting), or  using  a component observation ` such as `Observation.component code`  = LOINC 49541-6 (Fasting status - Reported).</t>
   </si>
   <si>
@@ -827,10 +815,7 @@
     <t>Specimen.processing</t>
   </si>
   <si>
-    <t>ステップの詳細を処理および処理します / Processing and processing step details</t>
-  </si>
-  <si>
-    <t>標本の処理と処理に関する詳細。 / Details concerning processing and processing steps for the specimen.</t>
+    <t>未使用</t>
   </si>
   <si>
     <t>.participation[typeCode=SBJ].act[code=SPCTRT, moodCode=EVN]</t>
@@ -903,12 +888,6 @@
     <t>Specimen.container</t>
   </si>
   <si>
-    <t>標本の直接容器（チューブ/スライドなど） / Direct container of specimen (tube/slide, etc.)</t>
-  </si>
-  <si>
-    <t>標本を保持している容器。コンテナの再帰的性質。つまり、ラックのトレイのチューブ内の血液はここでは対処されていません。 / The container holding the specimen.  The recursive nature of containers; i.e. blood in tube in tray in rack is not addressed here.</t>
-  </si>
-  <si>
     <t>.player.scopingRole[classCode=CONT].scoper</t>
   </si>
   <si>
@@ -1019,12 +998,6 @@
   </si>
   <si>
     <t>Specimen.condition</t>
-  </si>
-  <si>
-    <t>標本の状態 / State of the specimen</t>
-  </si>
-  <si>
-    <t>標本の性質を説明するモードまたは存在の状態。 / A mode or state of being that describes the nature of the specimen.</t>
   </si>
   <si>
     <t>標本の状態は、標本について行われた観察です。それはポイントインタイム評価です。特定のテストの品質または適切性を評価するために使用できます。 / Specimen condition is an observation made about the specimen.  It's a point-in-time assessment.  It can be used to assess its quality or appropriateness for a specific test.</t>
@@ -1372,7 +1345,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="66.4296875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="51.84375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -3212,10 +3185,10 @@
         <v>185</v>
       </c>
       <c r="M17" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="N17" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3280,7 +3253,7 @@
         <v>97</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>77</v>
@@ -3291,10 +3264,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3317,16 +3290,16 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="N18" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>192</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3376,7 +3349,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3391,21 +3364,21 @@
         <v>97</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AL18" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="AL18" t="s" s="2">
+      <c r="AM18" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>195</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3428,13 +3401,13 @@
         <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="L19" t="s" s="2">
-        <v>198</v>
-      </c>
       <c r="M19" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3485,7 +3458,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3500,21 +3473,21 @@
         <v>97</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3537,13 +3510,13 @@
         <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="L20" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3594,7 +3567,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3609,7 +3582,7 @@
         <v>77</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>77</v>
@@ -3620,10 +3593,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3652,7 +3625,7 @@
         <v>132</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>134</v>
@@ -3705,7 +3678,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3720,7 +3693,7 @@
         <v>136</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>77</v>
@@ -3731,14 +3704,14 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -3760,10 +3733,10 @@
         <v>131</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="N22" t="s" s="2">
         <v>134</v>
@@ -3818,7 +3791,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -3844,10 +3817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3870,13 +3843,13 @@
         <v>86</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3927,7 +3900,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -3942,21 +3915,21 @@
         <v>97</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="AL23" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>221</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3979,13 +3952,13 @@
         <v>86</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4036,7 +4009,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4051,21 +4024,21 @@
         <v>97</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>227</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4088,13 +4061,13 @@
         <v>86</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4145,7 +4118,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4163,7 +4136,7 @@
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
@@ -4171,10 +4144,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4197,13 +4170,13 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4254,7 +4227,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4269,21 +4242,21 @@
         <v>97</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4309,10 +4282,10 @@
         <v>162</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4342,10 +4315,10 @@
         <v>165</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>77</v>
@@ -4363,7 +4336,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4378,21 +4351,21 @@
         <v>97</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4418,13 +4391,13 @@
         <v>162</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4453,10 +4426,10 @@
         <v>165</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>77</v>
@@ -4474,7 +4447,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4489,21 +4462,21 @@
         <v>97</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4526,19 +4499,19 @@
         <v>86</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="O29" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="L29" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>77</v>
@@ -4563,13 +4536,13 @@
         <v>77</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>77</v>
@@ -4587,7 +4560,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4608,15 +4581,15 @@
         <v>77</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>258</v>
+        <v>254</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4639,13 +4612,13 @@
         <v>77</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4696,7 +4669,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4711,7 +4684,7 @@
         <v>97</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>77</v>
@@ -4722,10 +4695,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4748,13 +4721,13 @@
         <v>77</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="L31" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4805,7 +4778,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -4820,7 +4793,7 @@
         <v>77</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>77</v>
@@ -4831,10 +4804,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4863,7 +4836,7 @@
         <v>132</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="N32" t="s" s="2">
         <v>134</v>
@@ -4916,7 +4889,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -4931,7 +4904,7 @@
         <v>136</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>77</v>
@@ -4942,14 +4915,14 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -4971,10 +4944,10 @@
         <v>131</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>134</v>
@@ -5029,7 +5002,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5055,10 +5028,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5081,13 +5054,13 @@
         <v>77</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5138,7 +5111,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5153,7 +5126,7 @@
         <v>97</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>77</v>
@@ -5164,10 +5137,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5193,10 +5166,10 @@
         <v>162</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5226,10 +5199,10 @@
         <v>165</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>77</v>
@@ -5247,7 +5220,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5273,10 +5246,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5299,13 +5272,13 @@
         <v>77</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5356,7 +5329,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5371,21 +5344,21 @@
         <v>97</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>280</v>
+        <v>275</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5408,13 +5381,13 @@
         <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5465,7 +5438,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5480,7 +5453,7 @@
         <v>97</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>77</v>
@@ -5491,10 +5464,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5517,13 +5490,13 @@
         <v>77</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>285</v>
+        <v>256</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>286</v>
+        <v>256</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5574,7 +5547,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5589,7 +5562,7 @@
         <v>97</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>77</v>
@@ -5600,10 +5573,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5626,13 +5599,13 @@
         <v>77</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="L39" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5683,7 +5656,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -5698,7 +5671,7 @@
         <v>77</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>77</v>
@@ -5709,10 +5682,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5741,7 +5714,7 @@
         <v>132</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>134</v>
@@ -5794,7 +5767,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -5809,7 +5782,7 @@
         <v>136</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>77</v>
@@ -5820,14 +5793,14 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -5849,10 +5822,10 @@
         <v>131</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="N41" t="s" s="2">
         <v>134</v>
@@ -5907,7 +5880,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -5933,10 +5906,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5962,10 +5935,10 @@
         <v>143</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6016,7 +5989,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6037,15 +6010,15 @@
         <v>77</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>294</v>
+        <v>287</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6068,13 +6041,13 @@
         <v>77</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6125,7 +6098,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6140,7 +6113,7 @@
         <v>97</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>77</v>
@@ -6151,10 +6124,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6180,10 +6153,10 @@
         <v>162</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6213,10 +6186,10 @@
         <v>165</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>77</v>
@@ -6234,7 +6207,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6255,15 +6228,15 @@
         <v>77</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>304</v>
+        <v>297</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6286,13 +6259,13 @@
         <v>77</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6343,7 +6316,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6358,21 +6331,21 @@
         <v>97</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>309</v>
+        <v>302</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6395,13 +6368,13 @@
         <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6452,7 +6425,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6467,21 +6440,21 @@
         <v>97</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>314</v>
+        <v>307</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6504,13 +6477,13 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6540,10 +6513,10 @@
         <v>165</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>77</v>
@@ -6561,7 +6534,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -6576,21 +6549,21 @@
         <v>97</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>322</v>
+        <v>315</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6616,16 +6589,16 @@
         <v>162</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>324</v>
+        <v>256</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>325</v>
+        <v>256</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>77</v>
@@ -6650,13 +6623,13 @@
         <v>77</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>77</v>
@@ -6674,7 +6647,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -6695,15 +6668,15 @@
         <v>77</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>330</v>
+        <v>321</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6726,13 +6699,13 @@
         <v>77</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6783,7 +6756,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -6798,13 +6771,13 @@
         <v>97</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>335</v>
+        <v>326</v>
       </c>
     </row>
   </sheetData>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-specimen-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-specimen-pathology.xlsx
@@ -9,11 +9,14 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$57</definedName>
+  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1736" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2003" uniqueCount="366">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T12:51:50+00:00</t>
+    <t>2026-08-12T07:04:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>病理診断レポートにおいて臓器そのものを表現する検体情報を定義したプロファイル</t>
+    <t>このプロファイルはSpecimenリソースに対して、病理診断レポートにおいて臓器そのものを表現する検体情報のデータを送受信するための制約と拡張を定めたものである。</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -114,7 +117,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Specimen</t>
+    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_Specimen_Common</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -282,7 +285,7 @@
 </t>
   </si>
   <si>
-    <t>このアーティファクトの論理ID / Logical id of this artifact</t>
+    <t>論理ID</t>
   </si>
   <si>
     <t>リソースのURLで使用されるリソースの論理ID。割り当てられたら、この値は変更されません。 / The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
@@ -301,7 +304,7 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するMetadata / Metadata about the resource</t>
+    <t>リソースに関するメタデータ</t>
   </si>
   <si>
     <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
@@ -314,14 +317,186 @@
 </t>
   </si>
   <si>
-    <t>Specimen.implicitRules</t>
+    <t>Specimen.meta.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>エレメント相互参照のためのユニークID</t>
+  </si>
+  <si>
+    <t>リソース内の要素の固有ID（内部参照用）。これは、スペースを含まない任意の文字列値である可能性があります。</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Specimen.meta.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>実装によって定義される追加コンテンツ</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。</t>
+  </si>
+  <si>
+    <t>どのようなアプリケーション、プロジェクト、または標準が拡張機能を使用しているかに関わらず、拡張機能の使用には決して汚名が付くわけではありません - それらを使用または定義する機関または管轄区域に関係なく。拡張機能の使用こそが、FHIR仕様を誰にとっても簡単なコアレベルで維持することを可能にします。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>拡張子は常にURLで切り片にされます。</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
+ext-1:extensionまたはvalue[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Specimen.meta.versionId</t>
+  </si>
+  <si>
+    <t>バージョン固有のidentifier (Baajon koyū no shikibetsu-shi)</t>
+  </si>
+  <si>
+    <t>URLのバージョン部分に表示されるバージョン固有のidentifier。この値は、リソースが作成、更新、または削除された場合に変更されます。</t>
+  </si>
+  <si>
+    <t>サーバーがこの値を割り当て、クライアントが指定した値を無視する。ただし、サーバーが更新/削除時にバージョンの整合性を強制する場合を除く。</t>
+  </si>
+  <si>
+    <t>Meta.versionId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
+</t>
+  </si>
+  <si>
+    <t>Specimen.meta.lastUpdated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
+    <t>リソースのバージョンが最後に変更されたとき</t>
+  </si>
+  <si>
+    <t>リソースが最後に変更されたとき - 例えば、バージョンが変更されたとき。</t>
+  </si>
+  <si>
+    <t>この値はリソースが初めて作成される場合を除いて常に設定されています。サーバー/リソースマネージャーがこの値を設定します。クライアントが提供する値は関係ありません。これはHTTP Last-Modifiedに相当し、[read](http://hl7.org/fhir/R4/http.html#read)のインタラクションで同じ値を持つべきです。</t>
+  </si>
+  <si>
+    <t>Meta.lastUpdated</t>
+  </si>
+  <si>
+    <t>Specimen.meta.source</t>
   </si>
   <si>
     <t xml:space="preserve">uri
 </t>
   </si>
   <si>
-    <t>このコンテンツが作成されたルールのセット / A set of rules under which this content was created</t>
+    <t>リソースがどこから来たかを特定する</t>
+  </si>
+  <si>
+    <t>リソースのソースシステムを識別するURI。これにより、リソース内の情報のソースをトラックまたは区別するために使用できる最小限の[プロビナンス]（provenance.html＃）情報が提供されます。ソースは、別のFHIRサーバー、ドキュメント、メッセージ、データベースなどを識別できます。</t>
+  </si>
+  <si>
+    <t>プロバナンスのリソースにおいて、これはProvenance.entity.what[x]に対応します。ソースの正確な使用方法（および含意されるProvenance.entity.role）は実装者の判断に委ねられます。指定されたソースは1つだけです。追加のプロバナンスの詳細が必要な場合は、完全なプロバナンスリソースを使用するべきです。
+この要素は、正規のURLでホストされていないリソースの現在のマスターソースがどこにあるかを示すために使用できます。</t>
+  </si>
+  <si>
+    <t>Meta.source</t>
+  </si>
+  <si>
+    <t>Specimen.meta.profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>このリソースが適合を主張するプロファイル</t>
+  </si>
+  <si>
+    <t>このリソースが準拠すると主張する [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) リソースに関するプロファイルのリストです。URL は [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url) への参照です。</t>
+  </si>
+  <si>
+    <t>これらの主張が時間の経過に伴って検証または更新される方法と、それらを決定するサーバーや他の基盤に任されます。プロファイルURLのリストは1セットです。</t>
+  </si>
+  <si>
+    <t>Meta.profile</t>
+  </si>
+  <si>
+    <t>Specimen.meta.security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>このリソースに適用されたセキュリティラベル</t>
+  </si>
+  <si>
+    <t>このリソースにはセキュリティラベルが適用されています。これらのタグにより、特定のリソースが全体的なセキュリティポリシーやインフラストラクチャに関連付けられます。</t>
+  </si>
+  <si>
+    <t>セキュリティラベルは変更せずにリソースのバージョンを更新可能です。セキュリティラベルのリストはセットであり、一意性はシステム/コードに基づき、バージョンと表示は無視されます。</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>医療プライバシーおよびセキュリティ分類システムからのセキュリティラベル。</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
+  </si>
+  <si>
+    <t>Meta.security</t>
+  </si>
+  <si>
+    <t>Specimen.meta.tag</t>
+  </si>
+  <si>
+    <t>このリソースに適用されたタグ</t>
+  </si>
+  <si>
+    <t>このリソースに適用されるタグです。タグは、リソースをプロセスやワークフローに識別し、関連付けるために使用することが意図されており、アプリケーションはリソースの意味を解釈する際にタグを考慮する必要はありません。</t>
+  </si>
+  <si>
+    <t>リソースの表示バージョンを変更することなく、タグを更新できます。タグのリストは集合です。ユニーク性はシステム/コードに基づき、バージョンと表示は無視されます。</t>
+  </si>
+  <si>
+    <t>Meta.tag</t>
+  </si>
+  <si>
+    <t>Specimen.implicitRules</t>
+  </si>
+  <si>
+    <t>このコンテンツが作成されたセット</t>
   </si>
   <si>
     <t>リソースが構築されたときに従った一連のルールへの参照。コンテンツの処理時に理解する必要があります。多くの場合、これは他のプロファイルなどとともに特別なルールを定義する実装ガイドへの参照です。 / A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
@@ -340,7 +515,7 @@
 </t>
   </si>
   <si>
-    <t>リソースコンテンツの言語 / Language of the resource content</t>
+    <t>リソースコンテンツの言語</t>
   </si>
   <si>
     <t>リソースが書かれている基本言語。 / The base language in which the resource is written.</t>
@@ -352,10 +527,10 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>人間の言語。 / A human language.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>人間の言語</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -372,7 +547,7 @@
 </t>
   </si>
   <si>
-    <t>人間の解釈のためのリソースのテキスト概要 / Text summary of the resource, for human interpretation</t>
+    <t>このリソースを人間が解釈するためのテキスト要約</t>
   </si>
   <si>
     <t>リソースの概要を含み、人間へのリソースの内容を表すために使用できる人間の読み取り可能な叙述(Narative)。叙述(Narative)はすべての構造化されたデータをエンコードする必要はありませんが、人間が叙述(Narative)を読むだけで「臨床的に安全」にするために十分な詳細を含める必要があります。リソースの定義は、臨床的安全を確保するために、叙述(Narative)で表現するコンテンツを定義する場合があります。 / A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
@@ -398,7 +573,7 @@
 </t>
   </si>
   <si>
-    <t>インラインリソースが含まれています / Contained, inline Resources</t>
+    <t>インラインリソース含む</t>
   </si>
   <si>
     <t>これらのリソースには、それらを含むリソースを除いて独立した存在はありません - 独立して特定することはできず、独自の独立したトランザクションスコープを持つこともできません。 / These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
@@ -416,21 +591,10 @@
     <t>Specimen.extension</t>
   </si>
   <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>実装で定義された追加のコンテンツ / Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>リソースの基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>拡張機能を使用または定義する機関や管轄権に関係なく、アプリケーション、プロジェクト、または標準による拡張機能の使用に関連するスティグマはありません。拡張機能の使用は、FHIR仕様がすべての人にコアレベルのシンプルさを保持できるようにするものです。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+    <t>実装で定義された追加コンテンツ</t>
+  </si>
+  <si>
+    <t>An Extension</t>
   </si>
   <si>
     <t>DomainResource.extension</t>
@@ -443,15 +607,7 @@
     <t>Specimen.modifierExtension</t>
   </si>
   <si>
-    <t>無視できない拡張機能 / Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>リソースの基本的な定義の一部ではなく、それを含む要素の理解および/または含有要素の子孫の理解を変更するために使用される場合があります。通常、修飾子要素は否定または資格を提供します。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たされる一連の要件があります。アプリケーションの処理リソースは、修飾子拡張機能をチェックする必要があります。
-モディファイア拡張は、リソースまたはdomainResource上の要素の意味を変更してはなりません（修飾軸自体の意味を変更することはできません）。 / May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>修飾子拡張機能により、安全に無視できる大部分の拡張機能と明確に区別できるように、安全に無視できない拡張機能が可能になります。これにより、実装者が拡張の存在を禁止する必要性を排除することにより、相互運用性が促進されます。詳細については、[修飾子拡張の定義]（拡張性.html＃modifierextension）を参照してください。 / Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+    <t>無視できない拡張機能</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -500,7 +656,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>標本のステータス/可用性を提供するコード。 / Codes providing the status/availability of a specimen.</t>
+    <t>標本のステータス/可用性を提供するコード</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/specimen-status|4.0.1</t>
@@ -531,7 +687,7 @@
     <t>example</t>
   </si>
   <si>
-    <t>標本のタイプ。 / The type of the specimen.</t>
+    <t>標本のタイプ</t>
   </si>
   <si>
     <t>http://terminology.hl7.org/ValueSet/v2-0487</t>
@@ -641,44 +797,16 @@
     <t>Specimen.collection.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>要素間参照のための一意のID / Unique id for inter-element referencing</t>
-  </si>
-  <si>
     <t>リソース内の要素の一意のID（内部参照用）。これは、スペースを含まない文字列値である場合があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
   </si>
   <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Specimen.collection.extension</t>
   </si>
   <si>
-    <t>要素の基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
     <t>Specimen.collection.modifierExtension</t>
   </si>
   <si>
-    <t>extensions
-user contentmodifiers</t>
-  </si>
-  <si>
-    <t>認識されていなくても無視できない拡張機能 / Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>要素の基本的な定義の一部ではなく、それが含まれている要素の理解、および/または含まれる要素の子孫の理解を変更するために使用される場合があります。通常、修飾子要素は否定または資格を提供します。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。アプリケーションの処理リソースは、修飾子拡張機能をチェックする必要があります。
-モディファイア拡張は、リソースまたはdomainResource上の要素の意味を変更してはなりません（修飾軸自体の意味を変更することはできません）。 / May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+    <t>無視されてはいけない拡張</t>
   </si>
   <si>
     <t>BackboneElement.modifierExtension</t>
@@ -706,180 +834,174 @@
     <t>Specimen.collection.collected[x]</t>
   </si>
   <si>
+    <t>検体採取日時</t>
+  </si>
+  <si>
+    <t>.effectiveTime</t>
+  </si>
+  <si>
+    <t>FiveWs.init</t>
+  </si>
+  <si>
+    <t>SPM-17</t>
+  </si>
+  <si>
+    <t>Specimen.collection.duration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duration
+</t>
+  </si>
+  <si>
+    <t>検体採取期間</t>
+  </si>
+  <si>
+    <t>Specimen.collection.quantity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
+</t>
+  </si>
+  <si>
+    <t>検体量</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=SBJ].role[classCode=SPEC].player.quantity</t>
+  </si>
+  <si>
+    <t>SPM-12</t>
+  </si>
+  <si>
+    <t>Specimen.collection.method</t>
+  </si>
+  <si>
+    <t>採取方法</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/specimen-collection-method</t>
+  </si>
+  <si>
+    <t>.methodCode</t>
+  </si>
+  <si>
+    <t>SPM-7</t>
+  </si>
+  <si>
+    <t>Specimen.collection.bodySite</t>
+  </si>
+  <si>
+    <t>検体部位</t>
+  </si>
+  <si>
+    <t>ユースケースでは、ボディサイトをインラインコード化された要素の代わりに個別のリソースとして処理する必要がある場合（たとえば、個別に識別および追跡するため）、標準の拡張[BodySite]（Extension-BodySite.html）を使用します。 / If the use case requires  BodySite to be handled as a separate resource instead of an inline coded element (e.g. to identify and track separately)  then use the standard extension [bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
+  </si>
+  <si>
+    <t>採取部位</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+  </si>
+  <si>
+    <t>.targetSiteCode</t>
+  </si>
+  <si>
+    <t>SPM-8 and SPM-9</t>
+  </si>
+  <si>
+    <t>Specimen.collection.fastingStatus[x]</t>
+  </si>
+  <si>
+    <t>CodeableConcept
+Duration</t>
+  </si>
+  <si>
+    <t>この要素を使用して絶食ステータスを表すことは、2時間の尿-12時間の断食でのLOINC 2005-7（カルシウム[モル/時間]）などの「事前調整コード」を使用して観察することでそれを表現することを好むか、またはコンポーネントの観測 `などの` observation.component code` = loinc 49541-6（空腹時ステータス - 報告）。 / Representing fasting status using this element is preferred to representing it with an observation using a 'pre-coordinated code'  such as  LOINC 2005-7 (Calcium [Moles/​time] in 2 hour Urine --12 hours fasting), or  using  a component observation ` such as `Observation.component code`  = LOINC 49541-6 (Fasting status - Reported).</t>
+  </si>
+  <si>
+    <t>多くの診断テストでは、正確な解釈を容易にするために断食が必要です。 / Many diagnostic tests require fasting  to facilitate accurate interpretation.</t>
+  </si>
+  <si>
+    <t>患者の絶食状況</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/ValueSet/v2-0916</t>
+  </si>
+  <si>
+    <t>OBR-</t>
+  </si>
+  <si>
+    <t>Specimen.processing</t>
+  </si>
+  <si>
+    <t>未使用</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=SBJ].act[code=SPCTRT, moodCode=EVN]</t>
+  </si>
+  <si>
+    <t>Specimen.processing.id</t>
+  </si>
+  <si>
+    <t>Specimen.processing.extension</t>
+  </si>
+  <si>
+    <t>Specimen.processing.modifierExtension</t>
+  </si>
+  <si>
+    <t>Specimen.processing.description</t>
+  </si>
+  <si>
+    <t>手順のテキストによる説明</t>
+  </si>
+  <si>
+    <t>プロシジャー（処置等）のテキスト説明。 / Textual description of procedure.</t>
+  </si>
+  <si>
+    <t>.text</t>
+  </si>
+  <si>
+    <t>Specimen.processing.procedure</t>
+  </si>
+  <si>
+    <t>検体に適用される処理</t>
+  </si>
+  <si>
+    <t>試料の処理に使用されるプロシジャー（処置等）を指定するコード化された値。 / A coded value specifying the procedure used to process the specimen.</t>
+  </si>
+  <si>
+    <t>材料に対する処理</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/specimen-processing-procedure</t>
+  </si>
+  <si>
+    <t>Specimen.processing.additive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Substance|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>処理に使用される材料</t>
+  </si>
+  <si>
+    <t>処理ステップで使用される材料。 / Material used in the processing step.</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=CSM].role[classCode=ADTV].code</t>
+  </si>
+  <si>
+    <t>SPM-6</t>
+  </si>
+  <si>
+    <t>Specimen.processing.time[x]</t>
+  </si>
+  <si>
     <t>dateTime
 Period</t>
   </si>
   <si>
-    <t>検体採取日時</t>
-  </si>
-  <si>
-    <t>.effectiveTime</t>
-  </si>
-  <si>
-    <t>FiveWs.init</t>
-  </si>
-  <si>
-    <t>SPM-17</t>
-  </si>
-  <si>
-    <t>Specimen.collection.duration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Duration
-</t>
-  </si>
-  <si>
-    <t>検体採取期間</t>
-  </si>
-  <si>
-    <t>Specimen.collection.quantity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
-</t>
-  </si>
-  <si>
-    <t>検体量</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=SBJ].role[classCode=SPEC].player.quantity</t>
-  </si>
-  <si>
-    <t>SPM-12</t>
-  </si>
-  <si>
-    <t>Specimen.collection.method</t>
-  </si>
-  <si>
-    <t>採取方法</t>
-  </si>
-  <si>
-    <t>プロシジャー（処置等）の実行に使用される手法。 / The  technique that is used to perform the procedure.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/specimen-collection-method|4.0.1</t>
-  </si>
-  <si>
-    <t>.methodCode</t>
-  </si>
-  <si>
-    <t>SPM-7</t>
-  </si>
-  <si>
-    <t>Specimen.collection.bodySite</t>
-  </si>
-  <si>
-    <t>検体部位</t>
-  </si>
-  <si>
-    <t>ユースケースでは、ボディサイトをインラインコード化された要素の代わりに個別のリソースとして処理する必要がある場合（たとえば、個別に識別および追跡するため）、標準の拡張[BodySite]（Extension-BodySite.html）を使用します。 / If the use case requires  BodySite to be handled as a separate resource instead of an inline coded element (e.g. to identify and track separately)  then use the standard extension [bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
-  </si>
-  <si>
-    <t>解剖学的場所を説明するコード。左右性が含まれる場合があります。 / Codes describing anatomical locations. May include laterality.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
-  </si>
-  <si>
-    <t>.targetSiteCode</t>
-  </si>
-  <si>
-    <t>SPM-8 and SPM-9</t>
-  </si>
-  <si>
-    <t>Specimen.collection.fastingStatus[x]</t>
-  </si>
-  <si>
-    <t>CodeableConcept
-Duration</t>
-  </si>
-  <si>
-    <t>この要素を使用して絶食ステータスを表すことは、2時間の尿-12時間の断食でのLOINC 2005-7（カルシウム[モル/時間]）などの「事前調整コード」を使用して観察することでそれを表現することを好むか、またはコンポーネントの観測 `などの` observation.component code` = loinc 49541-6（空腹時ステータス - 報告）。 / Representing fasting status using this element is preferred to representing it with an observation using a 'pre-coordinated code'  such as  LOINC 2005-7 (Calcium [Moles/​time] in 2 hour Urine --12 hours fasting), or  using  a component observation ` such as `Observation.component code`  = LOINC 49541-6 (Fasting status - Reported).</t>
-  </si>
-  <si>
-    <t>多くの診断テストでは、正確な解釈を容易にするために断食が必要です。 / Many diagnostic tests require fasting  to facilitate accurate interpretation.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>患者の断食状況を説明するコード。 / Codes describing the fasting status of the patient.</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-0916</t>
-  </si>
-  <si>
-    <t>OBR-</t>
-  </si>
-  <si>
-    <t>Specimen.processing</t>
-  </si>
-  <si>
-    <t>未使用</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=SBJ].act[code=SPCTRT, moodCode=EVN]</t>
-  </si>
-  <si>
-    <t>Specimen.processing.id</t>
-  </si>
-  <si>
-    <t>Specimen.processing.extension</t>
-  </si>
-  <si>
-    <t>Specimen.processing.modifierExtension</t>
-  </si>
-  <si>
-    <t>Specimen.processing.description</t>
-  </si>
-  <si>
-    <t>プロシジャー（処置等）のテキスト説明 / Textual description of procedure</t>
-  </si>
-  <si>
-    <t>プロシジャー（処置等）のテキスト説明。 / Textual description of procedure.</t>
-  </si>
-  <si>
-    <t>.text</t>
-  </si>
-  <si>
-    <t>Specimen.processing.procedure</t>
-  </si>
-  <si>
-    <t>標本に適用される治療ステップを示します / Indicates the treatment step  applied to the specimen</t>
-  </si>
-  <si>
-    <t>試料の処理に使用されるプロシジャー（処置等）を指定するコード化された値。 / A coded value specifying the procedure used to process the specimen.</t>
-  </si>
-  <si>
-    <t>標本の処理に使用される手法を示すタイプ。 / Type indicating the technique used to process the specimen.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/specimen-processing-procedure|4.0.1</t>
-  </si>
-  <si>
-    <t>Specimen.processing.additive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Substance|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>処理ステップで使用される材料 / Material used in the processing step</t>
-  </si>
-  <si>
-    <t>処理ステップで使用される材料。 / Material used in the processing step.</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=CSM].role[classCode=ADTV].code</t>
-  </si>
-  <si>
-    <t>SPM-6</t>
-  </si>
-  <si>
-    <t>Specimen.processing.time[x]</t>
-  </si>
-  <si>
-    <t>標本処理の日時 / Date and time of specimen processing</t>
+    <t>検体を処理した日時あるいは期間のうちどちらか</t>
   </si>
   <si>
     <t>標本処理が発生した時間または期間の記録。たとえば、サンプル固定の時間またはサンプルがホルマリンにあった期間。 / A record of the time or period when the specimen processing occurred.  For example the time of sample fixation or the period of time the sample was in formalin.</t>
@@ -903,7 +1025,7 @@
     <t>Specimen.container.identifier</t>
   </si>
   <si>
-    <t>コンテナのID / Id for the container</t>
+    <t>採取容器のID</t>
   </si>
   <si>
     <t>コンテナ用のID。複数があるかもしれません。メーカーのバーコード、ラボに割り当てられたidentifierなど。コンテナIDは、状況によっては試料IDとは異なる場合があります。 / Id for container. There may be multiple; a manufacturer's bar code, lab assigned identifier, etc. The container ID may differ from the specimen id in some circumstances.</t>
@@ -915,7 +1037,7 @@
     <t>Specimen.container.description</t>
   </si>
   <si>
-    <t>コンテナのテキスト説明 / Textual description of the container</t>
+    <t>採取容器のテキストによる説明</t>
   </si>
   <si>
     <t>コンテナのテキスト説明。 / Textual description of the container.</t>
@@ -927,16 +1049,16 @@
     <t>Specimen.container.type</t>
   </si>
   <si>
-    <t>標本に直接関連する容器の種類 / Kind of container directly associated with specimen</t>
+    <t>検体に直接関係する採取容器の種類</t>
   </si>
   <si>
     <t>標本に関連付けられた容器の種類（例：スライド、アリコートなど）。 / The type of container associated with the specimen (e.g. slide, aliquot, etc.).</t>
   </si>
   <si>
-    <t>標本容器の種類。 / Type of specimen container.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/specimen-container-type|4.0.1</t>
+    <t>容器種別</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/specimen-container-type</t>
   </si>
   <si>
     <t>SPM-27</t>
@@ -945,7 +1067,7 @@
     <t>Specimen.container.capacity</t>
   </si>
   <si>
-    <t>コンテナボリュームまたはサイズ / Container volume or size</t>
+    <t>採取容器の容量あるいはサイズ</t>
   </si>
   <si>
     <t>容量（ボリュームまたはその他の測定）が含まれている場合があります。 / The capacity (volume or other measure) the container may contain.</t>
@@ -960,7 +1082,7 @@
     <t>Specimen.container.specimenQuantity</t>
   </si>
   <si>
-    <t>容器内の標本の量 / Quantity of specimen within container</t>
+    <t>検体採取量</t>
   </si>
   <si>
     <t>容器内の標本の量。試験片の種類に応じて、体積、寸法、またはその他の適切な測定値である場合があります。 / The quantity of specimen in the container; may be volume, dimensions, or other appropriate measurements, depending on the specimen type.</t>
@@ -979,13 +1101,13 @@
 Reference(Substance|4.0.1)</t>
   </si>
   <si>
-    <t>コンテナに関連付けられた添加剤 / Additive associated with container</t>
+    <t>採取容器の添加物（ CodeableConcept または Reference(Substance) のどちらか）</t>
   </si>
   <si>
     <t>標本を保存、維持、または強化するために物質を導入しました。例：ホルマリン、クエン酸塩、EDTA。 / Introduced substance to preserve, maintain or enhance the specimen. Examples: Formalin, Citrate, EDTA.</t>
   </si>
   <si>
-    <t>標本容器に追加された物質。 / Substance added to specimen container.</t>
+    <t>採取容器の添加物</t>
   </si>
   <si>
     <t>http://terminology.hl7.org/ValueSet/v2-0371</t>
@@ -1006,7 +1128,7 @@
     <t>標本の状態を使用して、特定のテストの品質または適切性を評価できます。 / The specimen condition can be used to assess its quality or appropriateness for a specific test.</t>
   </si>
   <si>
-    <t>標本の状態を説明するコード。 / Codes describing the state of the specimen.</t>
+    <t>材料の状態を説明するコード</t>
   </si>
   <si>
     <t>http://terminology.hl7.org/ValueSet/v2-0493</t>
@@ -1157,6 +1279,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -1332,7 +1469,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM49"/>
+  <dimension ref="A1:AM57"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="32.40234375" customWidth="true" bestFit="true"/>
@@ -1349,7 +1486,7 @@
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="109.33984375" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
@@ -1359,11 +1496,11 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="80.40625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="52.27734375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="34.8515625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="47.75" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="19.10546875" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="31.46875" customWidth="true" bestFit="true" hidden="true"/>
@@ -1494,7 +1631,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>31</v>
       </c>
@@ -1603,7 +1740,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>84</v>
       </c>
@@ -1714,7 +1851,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>92</v>
       </c>
@@ -1823,7 +1960,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>98</v>
       </c>
@@ -1845,10 +1982,10 @@
         <v>77</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K5" t="s" s="2">
         <v>99</v>
@@ -1859,9 +1996,7 @@
       <c r="M5" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="N5" t="s" s="2">
-        <v>102</v>
-      </c>
+      <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>77</v>
@@ -1910,7 +2045,7 @@
         <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
@@ -1922,10 +2057,10 @@
         <v>77</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="AL5" t="s" s="2">
         <v>77</v>
@@ -1934,7 +2069,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>104</v>
       </c>
@@ -1943,14 +2078,14 @@
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>77</v>
@@ -1962,16 +2097,16 @@
         <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -1997,46 +2132,46 @@
         <v>77</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="Y6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB6" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AC6" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="AD6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="AL6" t="s" s="2">
         <v>77</v>
@@ -2045,16 +2180,16 @@
         <v>77</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2070,10 +2205,10 @@
         <v>77</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>115</v>
+        <v>87</v>
       </c>
       <c r="L7" t="s" s="2">
         <v>116</v>
@@ -2144,10 +2279,10 @@
         <v>77</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>120</v>
+        <v>77</v>
       </c>
       <c r="AL7" t="s" s="2">
         <v>77</v>
@@ -2165,35 +2300,35 @@
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>122</v>
+        <v>77</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="I8" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>123</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>124</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>125</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>126</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2243,47 +2378,47 @@
         <v>77</v>
       </c>
       <c r="AF8" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="AG8" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ8" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM8" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" hidden="true">
+      <c r="A9" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="AG8" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH8" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK8" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="AL8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM8" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="2">
-        <v>129</v>
-      </c>
       <c r="B9" t="s" s="2">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>130</v>
+        <v>77</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>77</v>
@@ -2292,19 +2427,19 @@
         <v>77</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="M9" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="N9" t="s" s="2">
         <v>131</v>
-      </c>
-      <c r="L9" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>134</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2354,22 +2489,22 @@
         <v>77</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="AL9" t="s" s="2">
         <v>77</v>
@@ -2378,16 +2513,16 @@
         <v>77</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>130</v>
+        <v>77</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2400,26 +2535,24 @@
         <v>77</v>
       </c>
       <c r="I10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J10" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="J10" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="K10" t="s" s="2">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>77</v>
       </c>
@@ -2467,7 +2600,7 @@
         <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2479,10 +2612,10 @@
         <v>77</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>77</v>
@@ -2491,12 +2624,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2519,15 +2652,17 @@
         <v>86</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L11" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M11" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="N11" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="L11" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>77</v>
@@ -2552,13 +2687,13 @@
         <v>77</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>77</v>
+        <v>144</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>77</v>
+        <v>145</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>77</v>
+        <v>146</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>77</v>
@@ -2576,7 +2711,7 @@
         <v>77</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2588,19 +2723,19 @@
         <v>77</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>145</v>
+        <v>77</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>146</v>
+        <v>77</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>147</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
         <v>148</v>
       </c>
@@ -2616,7 +2751,7 @@
         <v>78</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>77</v>
@@ -2628,15 +2763,17 @@
         <v>86</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="L12" t="s" s="2">
         <v>149</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="N12" s="2"/>
+        <v>150</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>151</v>
+      </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>77</v>
@@ -2685,36 +2822,36 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>150</v>
+        <v>77</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>146</v>
+        <v>77</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>151</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2737,16 +2874,16 @@
         <v>86</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2772,31 +2909,31 @@
         <v>77</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>156</v>
+        <v>77</v>
       </c>
       <c r="Z13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF13" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -2811,21 +2948,21 @@
         <v>97</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM13" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" hidden="true">
+      <c r="A14" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="AL13" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="2">
-        <v>161</v>
-      </c>
       <c r="B14" t="s" s="2">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2845,19 +2982,19 @@
         <v>77</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="N14" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="L14" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -2883,31 +3020,31 @@
         <v>77</v>
       </c>
       <c r="X14" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="Z14" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="Y14" t="s" s="2">
+      <c r="AA14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF14" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="Z14" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AA14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>161</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -2922,25 +3059,25 @@
         <v>97</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>168</v>
+        <v>77</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>169</v>
+        <v>77</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>170</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>77</v>
+        <v>168</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -2956,21 +3093,21 @@
         <v>77</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="N15" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="L15" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N15" s="2"/>
-      <c r="O15" t="s" s="2">
-        <v>174</v>
-      </c>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>77</v>
       </c>
@@ -3018,7 +3155,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3033,32 +3170,32 @@
         <v>97</v>
       </c>
       <c r="AK15" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AL15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM15" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16" hidden="true">
+      <c r="A16" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="AL15" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>177</v>
-      </c>
       <c r="B16" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>77</v>
+        <v>176</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>77</v>
@@ -3067,18 +3204,20 @@
         <v>77</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="L16" t="s" s="2">
-        <v>179</v>
       </c>
       <c r="M16" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="N16" s="2"/>
+      <c r="N16" t="s" s="2">
+        <v>180</v>
+      </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>77</v>
@@ -3127,31 +3266,31 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>181</v>
+        <v>77</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>182</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
         <v>183</v>
       </c>
@@ -3179,17 +3318,15 @@
         <v>77</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="L17" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="M17" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="N17" t="s" s="2">
-        <v>186</v>
-      </c>
+      <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>77</v>
@@ -3238,7 +3375,7 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3250,10 +3387,10 @@
         <v>77</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>97</v>
+        <v>187</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>187</v>
+        <v>77</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>77</v>
@@ -3262,7 +3399,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
         <v>188</v>
       </c>
@@ -3284,23 +3421,21 @@
         <v>77</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="J18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="L18" t="s" s="2">
-        <v>190</v>
-      </c>
       <c r="M18" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>191</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>77</v>
@@ -3349,7 +3484,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3361,24 +3496,24 @@
         <v>77</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>97</v>
+        <v>187</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>192</v>
+        <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>193</v>
+        <v>77</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>194</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3389,7 +3524,7 @@
         <v>78</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>77</v>
@@ -3398,16 +3533,16 @@
         <v>77</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3458,13 +3593,13 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>77</v>
@@ -3473,21 +3608,21 @@
         <v>97</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>77</v>
+        <v>195</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3507,16 +3642,16 @@
         <v>77</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3567,7 +3702,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3579,56 +3714,56 @@
         <v>77</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>77</v>
+        <v>195</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>77</v>
+        <v>200</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>130</v>
+        <v>77</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>131</v>
+        <v>159</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>132</v>
+        <v>202</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>134</v>
+        <v>203</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3654,13 +3789,13 @@
         <v>77</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>77</v>
+        <v>204</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>77</v>
+        <v>205</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>77</v>
+        <v>206</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>77</v>
@@ -3678,72 +3813,70 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK21" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="AL21" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="AG21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH21" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ21" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AK21" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="AL21" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="AM21" t="s" s="2">
-        <v>77</v>
+        <v>209</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>210</v>
+        <v>77</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="J22" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>131</v>
+        <v>211</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M22" t="s" s="2">
         <v>212</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>77</v>
       </c>
@@ -3767,13 +3900,13 @@
         <v>77</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>77</v>
+        <v>214</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>77</v>
+        <v>215</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>77</v>
+        <v>216</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>77</v>
@@ -3791,36 +3924,36 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>128</v>
+        <v>217</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>77</v>
+        <v>218</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>77</v>
+        <v>219</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3843,16 +3976,18 @@
         <v>86</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
+      <c r="O23" t="s" s="2">
+        <v>223</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>77</v>
       </c>
@@ -3900,7 +4035,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -3915,21 +4050,21 @@
         <v>97</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>219</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3952,13 +4087,13 @@
         <v>86</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4009,7 +4144,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4024,21 +4159,21 @@
         <v>97</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>225</v>
+        <v>231</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4049,7 +4184,7 @@
         <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>77</v>
@@ -4058,18 +4193,20 @@
         <v>77</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>234</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>235</v>
+      </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4118,13 +4255,13 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>77</v>
@@ -4133,21 +4270,21 @@
         <v>97</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>77</v>
+        <v>236</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>224</v>
+        <v>77</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4158,7 +4295,7 @@
         <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>77</v>
@@ -4170,15 +4307,17 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -4227,13 +4366,13 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>77</v>
@@ -4242,21 +4381,21 @@
         <v>97</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>77</v>
+        <v>242</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>233</v>
+        <v>243</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4279,13 +4418,13 @@
         <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>162</v>
+        <v>245</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4312,13 +4451,13 @@
         <v>77</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>236</v>
+        <v>77</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>237</v>
+        <v>77</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>77</v>
@@ -4336,7 +4475,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4351,21 +4490,21 @@
         <v>97</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>239</v>
+        <v>248</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4388,17 +4527,15 @@
         <v>77</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>162</v>
+        <v>99</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>241</v>
+        <v>88</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>242</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>77</v>
@@ -4423,13 +4560,13 @@
         <v>77</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>243</v>
+        <v>77</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>244</v>
+        <v>77</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>77</v>
@@ -4447,7 +4584,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>240</v>
+        <v>102</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4459,24 +4596,24 @@
         <v>77</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>245</v>
+        <v>103</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>246</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4487,7 +4624,7 @@
         <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>77</v>
@@ -4496,23 +4633,19 @@
         <v>77</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>248</v>
+        <v>106</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>185</v>
+        <v>107</v>
       </c>
       <c r="M29" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="N29" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>250</v>
-      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>77</v>
       </c>
@@ -4536,60 +4669,60 @@
         <v>77</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>251</v>
+        <v>77</v>
       </c>
       <c r="Y29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF29" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AK29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="30" hidden="true">
+      <c r="A30" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="Z29" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="AG29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH29" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ29" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s" s="2">
-        <v>255</v>
-      </c>
       <c r="B30" t="s" s="2">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4606,19 +4739,19 @@
         <v>77</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>196</v>
+        <v>106</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>256</v>
+        <v>185</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4669,7 +4802,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4681,10 +4814,10 @@
         <v>77</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>97</v>
+        <v>187</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>257</v>
+        <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>77</v>
@@ -4693,12 +4826,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4718,16 +4851,16 @@
         <v>77</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>201</v>
+        <v>256</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>202</v>
+        <v>257</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>203</v>
+        <v>257</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4778,7 +4911,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>204</v>
+        <v>255</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -4790,35 +4923,35 @@
         <v>77</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>205</v>
+        <v>258</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>77</v>
+        <v>259</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>77</v>
+        <v>260</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>130</v>
+        <v>77</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>77</v>
@@ -4827,20 +4960,18 @@
         <v>77</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>131</v>
+        <v>227</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>132</v>
+        <v>262</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>134</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>77</v>
@@ -4889,72 +5020,68 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>208</v>
+        <v>261</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>205</v>
+        <v>263</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>77</v>
+        <v>264</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>77</v>
+        <v>265</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>210</v>
+        <v>77</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="J33" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>131</v>
+        <v>267</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>211</v>
+        <v>268</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>77</v>
       </c>
@@ -5002,36 +5129,36 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>213</v>
+        <v>266</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>77</v>
+        <v>264</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5054,13 +5181,13 @@
         <v>77</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>201</v>
+        <v>270</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5111,7 +5238,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5126,21 +5253,21 @@
         <v>97</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>77</v>
+        <v>273</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5163,13 +5290,13 @@
         <v>77</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>162</v>
+        <v>211</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5196,13 +5323,13 @@
         <v>77</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>165</v>
+        <v>214</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>77</v>
@@ -5220,7 +5347,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5235,21 +5362,21 @@
         <v>97</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>168</v>
+        <v>277</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>77</v>
+        <v>278</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5260,7 +5387,7 @@
         <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>77</v>
@@ -5272,15 +5399,17 @@
         <v>77</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>271</v>
+        <v>211</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>280</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>281</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -5305,13 +5434,13 @@
         <v>77</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>77</v>
+        <v>214</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>77</v>
+        <v>282</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>77</v>
+        <v>283</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>77</v>
@@ -5329,13 +5458,13 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>77</v>
@@ -5344,21 +5473,21 @@
         <v>97</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>275</v>
+        <v>285</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5378,19 +5507,23 @@
         <v>77</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>221</v>
+        <v>287</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>277</v>
+        <v>234</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
+        <v>234</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>289</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>77</v>
       </c>
@@ -5414,13 +5547,13 @@
         <v>77</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>77</v>
+        <v>144</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>77</v>
+        <v>290</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>77</v>
+        <v>291</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>77</v>
@@ -5438,7 +5571,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5453,21 +5586,21 @@
         <v>97</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>223</v>
+        <v>77</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>77</v>
+        <v>292</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5490,13 +5623,13 @@
         <v>77</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>196</v>
+        <v>245</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>256</v>
+        <v>294</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>256</v>
+        <v>294</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5547,7 +5680,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5562,7 +5695,7 @@
         <v>97</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>280</v>
+        <v>295</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>77</v>
@@ -5571,12 +5704,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5599,13 +5732,13 @@
         <v>77</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>201</v>
+        <v>99</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>202</v>
+        <v>88</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>203</v>
+        <v>250</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5656,7 +5789,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>204</v>
+        <v>102</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -5671,7 +5804,7 @@
         <v>77</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>205</v>
+        <v>103</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>77</v>
@@ -5680,16 +5813,16 @@
         <v>77</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>282</v>
+        <v>297</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>282</v>
+        <v>297</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>130</v>
+        <v>77</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -5708,17 +5841,15 @@
         <v>77</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>134</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>77</v>
@@ -5767,7 +5898,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>208</v>
+        <v>113</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -5779,10 +5910,10 @@
         <v>77</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>136</v>
+        <v>187</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>205</v>
+        <v>77</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>77</v>
@@ -5791,16 +5922,16 @@
         <v>77</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>283</v>
+        <v>298</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>283</v>
+        <v>298</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>210</v>
+        <v>77</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -5819,20 +5950,16 @@
         <v>86</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>211</v>
+        <v>253</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>77</v>
       </c>
@@ -5880,7 +6007,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>213</v>
+        <v>254</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -5892,10 +6019,10 @@
         <v>77</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>136</v>
+        <v>187</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>77</v>
@@ -5904,12 +6031,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>284</v>
+        <v>299</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>284</v>
+        <v>299</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5920,7 +6047,7 @@
         <v>78</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>77</v>
@@ -5929,16 +6056,16 @@
         <v>77</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>143</v>
+        <v>99</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>286</v>
+        <v>301</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5989,13 +6116,13 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>284</v>
+        <v>299</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>77</v>
@@ -6004,21 +6131,21 @@
         <v>97</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>145</v>
+        <v>302</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>287</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6041,13 +6168,13 @@
         <v>77</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>289</v>
+        <v>304</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6074,13 +6201,13 @@
         <v>77</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>77</v>
+        <v>214</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>77</v>
+        <v>306</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>77</v>
+        <v>307</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>77</v>
@@ -6098,7 +6225,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6113,7 +6240,7 @@
         <v>97</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>291</v>
+        <v>217</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>77</v>
@@ -6122,12 +6249,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6138,7 +6265,7 @@
         <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>77</v>
@@ -6150,13 +6277,13 @@
         <v>77</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>162</v>
+        <v>309</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>293</v>
+        <v>310</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>294</v>
+        <v>311</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6183,13 +6310,13 @@
         <v>77</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>295</v>
+        <v>77</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>296</v>
+        <v>77</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>77</v>
@@ -6207,13 +6334,13 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>77</v>
@@ -6222,21 +6349,21 @@
         <v>97</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>168</v>
+        <v>312</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>297</v>
+        <v>313</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>298</v>
+        <v>314</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>298</v>
+        <v>314</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6259,13 +6386,13 @@
         <v>77</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>230</v>
+        <v>315</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>299</v>
+        <v>316</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>300</v>
+        <v>317</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6316,7 +6443,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>298</v>
+        <v>314</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6331,21 +6458,21 @@
         <v>97</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>301</v>
+        <v>263</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>302</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6356,7 +6483,7 @@
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>77</v>
@@ -6368,13 +6495,13 @@
         <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6425,13 +6552,13 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>77</v>
@@ -6440,21 +6567,21 @@
         <v>97</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>307</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6477,13 +6604,13 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>309</v>
+        <v>99</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>310</v>
+        <v>88</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>311</v>
+        <v>250</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6510,13 +6637,13 @@
         <v>77</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>312</v>
+        <v>77</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>313</v>
+        <v>77</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>77</v>
@@ -6534,7 +6661,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>308</v>
+        <v>102</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -6546,24 +6673,24 @@
         <v>77</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>314</v>
+        <v>103</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>315</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6583,23 +6710,19 @@
         <v>77</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>162</v>
+        <v>106</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>256</v>
+        <v>107</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>318</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>77</v>
       </c>
@@ -6623,13 +6746,13 @@
         <v>77</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>251</v>
+        <v>77</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>319</v>
+        <v>77</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>320</v>
+        <v>77</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>77</v>
@@ -6647,7 +6770,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>316</v>
+        <v>113</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -6659,7 +6782,7 @@
         <v>77</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>97</v>
+        <v>187</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>77</v>
@@ -6668,10 +6791,10 @@
         <v>77</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>321</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
         <v>322</v>
       </c>
@@ -6693,19 +6816,19 @@
         <v>77</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>323</v>
+        <v>106</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>324</v>
+        <v>253</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>324</v>
+        <v>185</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6756,7 +6879,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>322</v>
+        <v>254</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -6768,19 +6891,913 @@
         <v>77</v>
       </c>
       <c r="AJ49" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="50" hidden="true">
+      <c r="A50" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
+      <c r="P50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AK49" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM49" t="s" s="2">
+      <c r="AK50" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM50" t="s" s="2">
         <v>326</v>
+      </c>
+    </row>
+    <row r="51" hidden="true">
+      <c r="A51" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
+      <c r="P51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q51" s="2"/>
+      <c r="R51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="52" hidden="true">
+      <c r="A52" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
+      <c r="P52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="53" hidden="true">
+      <c r="A53" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
+      <c r="P53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="54" hidden="true">
+      <c r="A54" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
+      <c r="P54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="55" hidden="true">
+      <c r="A55" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
+      <c r="P55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="56" hidden="true">
+      <c r="A56" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="P56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="57" hidden="true">
+      <c r="A57" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
+      <c r="P57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>365</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AM57">
+    <filterColumn colId="7">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="27">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI56">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-specimen-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-specimen-pathology.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T07:04:31+00:00</t>
+    <t>2026-08-12T07:45:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-specimen-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-specimen-pathology.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T07:45:23+00:00</t>
+    <t>2026-08-12T12:14:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-specimen-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-specimen-pathology.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T12:14:47+00:00</t>
+    <t>2026-08-12T12:53:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-specimen-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-specimen-pathology.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T12:53:42+00:00</t>
+    <t>2026-08-12T13:21:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-specimen-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-specimen-pathology.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T13:21:20+00:00</t>
+    <t>2026-08-13T00:17:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-specimen-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-specimen-pathology.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T00:17:30+00:00</t>
+    <t>2026-08-13T00:49:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-specimen-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-specimen-pathology.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T00:49:15+00:00</t>
+    <t>2026-08-13T01:04:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-specimen-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-specimen-pathology.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T01:04:13+00:00</t>
+    <t>2026-08-13T01:37:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-specimen-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-specimen-pathology.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T01:37:50+00:00</t>
+    <t>2026-08-13T08:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-specimen-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-specimen-pathology.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T08:49:13+00:00</t>
+    <t>2026-08-13T13:00:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-specimen-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-specimen-pathology.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T13:00:31+00:00</t>
+    <t>2026-08-13T13:31:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-specimen-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-specimen-pathology.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T13:31:56+00:00</t>
+    <t>2026-08-13T23:21:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-specimen-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-specimen-pathology.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T23:21:35+00:00</t>
+    <t>2026-08-13T23:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-specimen-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-specimen-pathology.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T23:54:59+00:00</t>
+    <t>2026-08-19T04:30:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
